--- a/02_DIA_inicio_2026_analisis_assets/rbd_9446_escuela-de-parvulos-rayito-de-luz_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9446_escuela-de-parvulos-rayito-de-luz_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10F58522-9FE2-4FF9-8ABA-21C5597032DD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E8026B5-328C-49D7-8CED-3DEF37EBCA41}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1C9CFFE-F37E-4641-97B1-643525FEB00F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B17CF35-5413-41BF-B1B3-3D72030FAC51}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D010FC9-150A-48AF-A131-ADDAE6027C7D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A86940C3-13F7-402F-BD1F-E61F7B5C6100}"/>
 </file>